--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_341_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_341_R35.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6433</v>
+        <v>4.5371</v>
       </c>
       <c r="E2" t="n">
-        <v>4.21</v>
+        <v>5.6249</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4333</v>
+        <v>-1.0878</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.1655</v>
+        <v>5.3897</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.1418</v>
+        <v>-0.904</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.0238</v>
+        <v>6.2936</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.4106</v>
+        <v>7.5414</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.6548</v>
+        <v>-0.124</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2442</v>
+        <v>7.6654</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.755</v>
+        <v>-2.1517</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.487</v>
+        <v>-0.78</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.2679</v>
+        <v>-1.3717</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.3917</v>
+        <v>-4.871</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3423</v>
+        <v>-0.3038</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7957</v>
+        <v>0.8101</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4533</v>
+        <v>-1.1138</v>
       </c>
       <c r="V2" t="n">
-        <v>3.0748</v>
+        <v>2.0026</v>
       </c>
       <c r="W2" t="n">
-        <v>3.2166</v>
+        <v>2.1444</v>
       </c>
       <c r="X2" t="n">
         <v>-0.1418</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3433</v>
+        <v>3.3683</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5319</v>
+        <v>3.1366</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1886</v>
+        <v>0.2317</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3897</v>
+        <v>-2.1655</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.904</v>
+        <v>-1.1418</v>
       </c>
       <c r="I3" t="n">
-        <v>6.2936</v>
+        <v>-1.0238</v>
       </c>
       <c r="J3" t="n">
-        <v>7.5414</v>
+        <v>-0.4106</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.124</v>
+        <v>-0.6548</v>
       </c>
       <c r="L3" t="n">
-        <v>7.6654</v>
+        <v>0.2442</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1517</v>
+        <v>-1.755</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.78</v>
+        <v>-0.487</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3717</v>
+        <v>-1.2679</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.871</v>
+        <v>-1.3917</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3195</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4976</v>
+        <v>1.0673</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2829</v>
+        <v>1.7223</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2147</v>
+        <v>-0.655</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0026</v>
+        <v>3.0748</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>3.2166</v>
       </c>
       <c r="X3" t="n">
         <v>-0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7423</v>
+        <v>3.1304</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9424</v>
+        <v>3.5321</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2</v>
+        <v>-0.4017</v>
       </c>
       <c r="G4" t="n">
         <v>4.6868</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2486</v>
+        <v>0.1395</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2082</v>
+        <v>0.3815</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0404</v>
+        <v>-0.242</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0119</v>
+        <v>2.9766</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6007</v>
+        <v>4.2965</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5887</v>
+        <v>-1.3199</v>
       </c>
       <c r="G5" t="n">
         <v>4.5904</v>
@@ -844,13 +844,13 @@
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.434</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.586</v>
+        <v>1.2819</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.02</v>
+        <v>-0.7512</v>
       </c>
       <c r="V5" t="n">
         <v>-2.1444</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9813</v>
+        <v>2.3563</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0979</v>
+        <v>2.204</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1165</v>
+        <v>0.1523</v>
       </c>
       <c r="G6" t="n">
         <v>-1.3581</v>
@@ -922,13 +922,13 @@
         <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2689</v>
+        <v>0.1061</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9911</v>
+        <v>1.0971</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2599</v>
+        <v>-0.9911</v>
       </c>
       <c r="V6" t="n">
         <v>2.6805</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8411999999999999</v>
+        <v>1.0534</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9541</v>
+        <v>1.484</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1129</v>
+        <v>-0.4306</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5629</v>
+        <v>-1.0382</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.605</v>
+        <v>-0.6601</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1678</v>
+        <v>-0.3781</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7702</v>
+        <v>-0.6055</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6652</v>
+        <v>0.0336</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4354</v>
+        <v>-0.6391</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2073</v>
+        <v>-0.4327</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0602</v>
+        <v>-0.6938</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2676</v>
+        <v>0.261</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8145</v>
+        <v>0.1612</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9673</v>
+        <v>-0.0549</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1529</v>
+        <v>0.2161</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5361</v>
+        <v>1.4665</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6083</v>
+        <v>2.1444</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1444</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7428</v>
+        <v>0.7613</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1734</v>
+        <v>2.0139</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4306</v>
+        <v>-1.2526</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0382</v>
+        <v>-1.1983</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6601</v>
+        <v>-3.3096</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3781</v>
+        <v>2.1113</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6055</v>
+        <v>0.1709</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0336</v>
+        <v>-2.2582</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6391</v>
+        <v>2.4291</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4327</v>
+        <v>-1.3692</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6938</v>
+        <v>-1.0514</v>
       </c>
       <c r="O8" t="n">
-        <v>0.261</v>
+        <v>-0.3178</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1494</v>
+        <v>0.9416</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3655</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2161</v>
+        <v>0.1709</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4665</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5014999999999999</v>
+        <v>0.3529</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8212</v>
+        <v>1.6002</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3198</v>
+        <v>-1.2473</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1983</v>
+        <v>0.5629</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.3096</v>
+        <v>-0.605</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1113</v>
+        <v>1.1678</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1709</v>
+        <v>0.7702</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.2582</v>
+        <v>-0.6652</v>
       </c>
       <c r="L9" t="n">
-        <v>2.4291</v>
+        <v>1.4354</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3692</v>
+        <v>-0.2073</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0514</v>
+        <v>0.0602</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3178</v>
+        <v>-0.2676</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6818</v>
+        <v>0.3262</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.6135</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1037</v>
+        <v>-0.2873</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.214</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6545</v>
+        <v>-1.0591</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7416</v>
+        <v>-1.2134</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0871</v>
+        <v>0.1544</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5682</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6818</v>
+        <v>0.2772</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7943</v>
+        <v>0.3224</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3266</v>
+        <v>-2.5305</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6677</v>
+        <v>-1.6363</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.659</v>
+        <v>-0.8942</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6337</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.771</v>
+        <v>0.5671</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3383</v>
+        <v>0.3697</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4327</v>
+        <v>0.1975</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8265</v>
+        <v>14.9467</v>
       </c>
       <c r="E12" t="n">
-        <v>19.9223</v>
+        <v>21.0425</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.095699999999999</v>
+        <v>-6.0957</v>
       </c>
       <c r="G12" t="n">
         <v>5.267799999999999</v>
@@ -1390,13 +1390,13 @@
         <v>15.0769</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6929</v>
+        <v>3.8131</v>
       </c>
       <c r="T12" t="n">
-        <v>6.1942</v>
+        <v>7.3143</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.501199999999999</v>
+        <v>-3.5011</v>
       </c>
       <c r="V12" t="n">
         <v>5.866000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4224</v>
+        <v>1.995</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4788</v>
+        <v>2.9506</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0564</v>
+        <v>-0.9556</v>
       </c>
       <c r="G13" t="n">
         <v>0.659</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0742</v>
+        <v>0.4984</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1415</v>
+        <v>0.3304</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V13" t="n">
         <v>0.1418</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. MUTAF</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1816</v>
+        <v>1.2323</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7285</v>
+        <v>1.5145</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4531</v>
+        <v>-0.2821</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1633</v>
+        <v>-0.9539</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1633</v>
+        <v>2.516</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-3.4698</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0168</v>
+        <v>0.5074</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0168</v>
+        <v>0.4005</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.1069</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1465</v>
+        <v>-1.4612</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1465</v>
+        <v>2.1155</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-3.5767</v>
       </c>
       <c r="P14" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5544</v>
+        <v>0.114</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7117</v>
+        <v>0.7905</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1573</v>
+        <v>-0.6765</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>D. MUTAF</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.848</v>
+        <v>0.7098</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0422</v>
+        <v>0.2567</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.1942</v>
+        <v>0.4531</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7321</v>
+        <v>0.1633</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8797</v>
+        <v>0.1633</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1476</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.883</v>
+        <v>0.0168</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6622</v>
+        <v>0.0168</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2208</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1509</v>
+        <v>0.1465</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2175</v>
+        <v>0.1465</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3684</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>2.884</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5662</v>
+        <v>0.2399</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6822</v>
+        <v>-0.1573</v>
       </c>
       <c r="V15" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6755</v>
+        <v>-0.3084</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1606</v>
+        <v>-0.6939</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4851</v>
+        <v>0.3855</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9539</v>
+        <v>-0.4236</v>
       </c>
       <c r="H16" t="n">
-        <v>2.516</v>
+        <v>1.5606</v>
       </c>
       <c r="I16" t="n">
-        <v>-3.4698</v>
+        <v>-1.9842</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5074</v>
+        <v>-0.6274</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4005</v>
+        <v>0.3564</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1069</v>
+        <v>-0.9838</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4612</v>
+        <v>0.2039</v>
       </c>
       <c r="N16" t="n">
-        <v>2.1155</v>
+        <v>1.2042</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.5767</v>
+        <v>-1.0004</v>
       </c>
       <c r="P16" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4428</v>
+        <v>-0.4905</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4367</v>
+        <v>-0.2082</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8794999999999999</v>
+        <v>-0.2822</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5662</v>
+        <v>-0.371</v>
       </c>
       <c r="E17" t="n">
-        <v>1.843</v>
+        <v>0.5455</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2768</v>
+        <v>-0.9166</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6542</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4523</v>
+        <v>0.5151</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8521</v>
+        <v>0.5546</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3998</v>
+        <v>-0.0395</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6565</v>
+        <v>-0.7071</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6939</v>
+        <v>0.9162</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0374</v>
+        <v>-1.6232</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4236</v>
+        <v>1.3354</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5606</v>
+        <v>-0.3577</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9842</v>
+        <v>1.693</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6274</v>
+        <v>3.1369</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3564</v>
+        <v>0.39</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9838</v>
+        <v>2.7469</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2039</v>
+        <v>-1.8016</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2042</v>
+        <v>-0.7477</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0004</v>
+        <v>-1.0539</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8386</v>
+        <v>0.1199</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2082</v>
+        <v>-0.0431</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6304</v>
+        <v>0.163</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1418</v>
+        <v>-1.4665</v>
       </c>
       <c r="W18" t="n">
         <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2461</v>
+        <v>-0.8875</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4444</v>
+        <v>1.5863</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6904</v>
+        <v>-2.4738</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3354</v>
+        <v>1.712</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3577</v>
+        <v>2.0432</v>
       </c>
       <c r="I19" t="n">
-        <v>1.693</v>
+        <v>-0.3312</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1369</v>
+        <v>1.2152</v>
       </c>
       <c r="K19" t="n">
-        <v>0.39</v>
+        <v>0.8605</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7469</v>
+        <v>0.3546</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8016</v>
+        <v>0.4968</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7477</v>
+        <v>1.1827</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0539</v>
+        <v>-0.6859</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4191</v>
+        <v>-0.919</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5149</v>
+        <v>-0.165</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0958</v>
+        <v>-0.7541</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4665</v>
+        <v>-2.1444</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5109</v>
+        <v>-1.225</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4683</v>
+        <v>1.8011</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9792</v>
+        <v>-3.0261</v>
       </c>
       <c r="G20" t="n">
-        <v>1.712</v>
+        <v>1.7321</v>
       </c>
       <c r="H20" t="n">
-        <v>2.0432</v>
+        <v>2.8797</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3312</v>
+        <v>-1.1476</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2152</v>
+        <v>2.883</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8605</v>
+        <v>2.6622</v>
       </c>
       <c r="L20" t="n">
-        <v>0.3546</v>
+        <v>0.2208</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4968</v>
+        <v>-1.1509</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1827</v>
+        <v>0.2175</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6859</v>
+        <v>-1.3684</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5424</v>
+        <v>0.8109</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2829</v>
+        <v>1.3251</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2595</v>
+        <v>-0.5142</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1444</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.6805</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.0894</v>
+        <v>-1.4838</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4637</v>
+        <v>0.244</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.6257</v>
+        <v>-1.7277</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0009</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.2149</v>
+        <v>-0.6093</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5816</v>
+        <v>0.1261</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6333</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>2.8223</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8692</v>
+        <v>-2.9123</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2069</v>
+        <v>-1.2801</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6622</v>
+        <v>-1.6322</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6347</v>
+        <v>-4.7102</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1621</v>
+        <v>-2.3781</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7968</v>
+        <v>-2.3322</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2515</v>
+        <v>-1.4759</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8907</v>
+        <v>-2.406</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6391</v>
+        <v>0.93</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8862</v>
+        <v>-3.2343</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2714</v>
+        <v>0.0279</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.1577</v>
+        <v>-3.2622</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.554</v>
+        <v>0.2438</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>0.5153</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2552</v>
+        <v>-0.2715</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.6805</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.6805</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8762</v>
+        <v>-3.1786</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5679</v>
+        <v>-0.6172</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.3083</v>
+        <v>-2.5614</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4919</v>
+        <v>-0.6347</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1405</v>
+        <v>1.1621</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6323</v>
+        <v>-1.7968</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8234</v>
+        <v>0.2515</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8234</v>
+        <v>0.8907</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.6391</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3153</v>
+        <v>-0.8862</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6830000000000001</v>
+        <v>0.2714</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6323</v>
+        <v>-1.1577</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3818</v>
+        <v>0.1366</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3734</v>
+        <v>0.291</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0083</v>
+        <v>-0.1544</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.5387</v>
+        <v>-2.6805</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>-2.6805</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.272</v>
+        <v>-3.5446</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4596</v>
+        <v>-0.45</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8123</v>
+        <v>-3.0946</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.7102</v>
+        <v>-0.4919</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.3781</v>
+        <v>0.1405</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3322</v>
+        <v>-0.6323</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.4759</v>
+        <v>0.8234</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.406</v>
+        <v>0.8234</v>
       </c>
       <c r="L24" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2343</v>
+        <v>-1.3153</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0279</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.2622</v>
+        <v>-0.6323</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5515</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1158</v>
+        <v>-0.0501</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6642</v>
+        <v>-0.2555</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4516</v>
+        <v>0.2054</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3943</v>
+        <v>-2.5387</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.8266</v>
+        <v>-10.6812</v>
       </c>
       <c r="E25" t="n">
-        <v>6.773800000000001</v>
+        <v>6.773699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.6001</v>
+        <v>-17.4547</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.267600000000001</v>
+        <v>-5.267600000000003</v>
       </c>
       <c r="H25" t="n">
         <v>12.0646</v>
@@ -2380,7 +2380,7 @@
         <v>10.671</v>
       </c>
       <c r="K25" t="n">
-        <v>6.690199999999999</v>
+        <v>6.690200000000001</v>
       </c>
       <c r="L25" t="n">
         <v>3.980700000000001</v>
@@ -2395,7 +2395,7 @@
         <v>-21.313</v>
       </c>
       <c r="P25" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-9.999999999976694e-05</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.077</v>
@@ -2404,16 +2404,16 @@
         <v>15.077</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.6929</v>
+        <v>0.4524000000000002</v>
       </c>
       <c r="T25" t="n">
-        <v>3.501299999999999</v>
+        <v>3.5011</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.194100000000001</v>
+        <v>-3.0487</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.866</v>
+        <v>-5.866000000000001</v>
       </c>
       <c r="W25" t="n">
         <v>7.6783</v>
